--- a/Gstsaralprotesting/src/test/java/pro/saral/testData/BLRB00769G-TDSForm24Q1.xlsx
+++ b/Gstsaralprotesting/src/test/java/pro/saral/testData/BLRB00769G-TDSForm24Q1.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujatha\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55209906-9415-4031-9D70-D0CE796CAA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="601" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="601"/>
   </bookViews>
   <sheets>
     <sheet name="Deductor" sheetId="47" r:id="rId1"/>
@@ -19,360 +13,8 @@
     <sheet name="Deduction Details" sheetId="46" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Kiranss</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Name of the Company</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>TAN of your Company.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Select Financial Year  From the List</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Select Quarter from the list.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>PAN of the Company</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Name of the Person responsible for Deducting / Collecting and remitting the tax at source</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>PAN of the Responsible Person</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Designation of the person mentioned in the previous field</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Kiranss</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Running Serial No of the Deductions</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>The unique serial no w. r. t. Employee names.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>It will be the Serial No as seen in Employee Master Screen</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Valid PAN Number or PANAPPLIED or PANNOTAVBL or PANINVALID
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Either beginning of Financial Year or Date of Joining, whichever is LATER.
-Should be within the Financial Year.
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Either end of Financial Year or Date of Leaving, whichever isEARLIER.
-Should be within the Financial Year.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Date of Amount Paid to the Party. Format: dd/mm/yyyy</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amount of Income Tax deducted in Total TDS</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amount of Education Cess deducted in Total TDS</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Date on Which Tax is Deducted. Format: dd/mm/yyyy</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1458,13 +1100,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="0.00;[Red]0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mmm/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1476,32 +1118,6 @@
       <sz val="8"/>
       <color indexed="10"/>
       <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -1640,19 +1256,19 @@
   </borders>
   <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -1664,72 +1280,72 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="13" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="13" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="13" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="13" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="13" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 2 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 6" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 7" xfId="13" xr:uid="{444522E7-8628-4116-AF22-032530513915}"/>
-    <cellStyle name="Style 1" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Style 1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Style 1 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Style 1 4" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Style 1 5" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Style 1 6" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 3" xfId="3"/>
+    <cellStyle name="Normal 2 4" xfId="4"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Normal 6" xfId="6"/>
+    <cellStyle name="Normal 7" xfId="13"/>
+    <cellStyle name="Style 1" xfId="7"/>
+    <cellStyle name="Style 1 2" xfId="8"/>
+    <cellStyle name="Style 1 3" xfId="9"/>
+    <cellStyle name="Style 1 4" xfId="10"/>
+    <cellStyle name="Style 1 5" xfId="11"/>
+    <cellStyle name="Style 1 6" xfId="12"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2091,9 +1707,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AD61"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="38.7109375" customWidth="1"/>
@@ -2103,33 +1719,33 @@
     <col min="28" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:30">
+      <c r="A1" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="19"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="B1" s="26"/>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30">
       <c r="A3" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30">
       <c r="A4" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
       <c r="AA4" t="s">
@@ -2143,11 +1759,11 @@
       </c>
       <c r="AD4" s="16"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30">
       <c r="A5" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>219</v>
       </c>
       <c r="AA5" t="s">
@@ -2160,11 +1776,11 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30">
       <c r="A6" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>185</v>
       </c>
       <c r="AA6" t="s">
@@ -2177,11 +1793,11 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:30">
+      <c r="A7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="19"/>
+      <c r="B7" s="26"/>
       <c r="AA7" t="s">
         <v>61</v>
       </c>
@@ -2192,11 +1808,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30">
       <c r="A8" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>222</v>
       </c>
       <c r="AA8" t="s">
@@ -2209,11 +1825,11 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30">
       <c r="A9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="22"/>
       <c r="AA9" t="s">
         <v>63</v>
       </c>
@@ -2224,11 +1840,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30">
       <c r="A10" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>223</v>
       </c>
       <c r="AA10" t="s">
@@ -2241,11 +1857,11 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30">
       <c r="A11" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>224</v>
       </c>
       <c r="AA11" t="s">
@@ -2258,11 +1874,11 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30">
       <c r="A12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="20"/>
       <c r="AA12" t="s">
         <v>66</v>
       </c>
@@ -2273,11 +1889,11 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30">
       <c r="A13" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>225</v>
       </c>
       <c r="AA13" t="s">
@@ -2290,11 +1906,11 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30">
       <c r="A14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>226</v>
       </c>
       <c r="AA14" t="s">
@@ -2307,11 +1923,11 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30">
       <c r="A15" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>227</v>
       </c>
       <c r="AA15" t="s">
@@ -2324,11 +1940,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30">
       <c r="A16" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>145</v>
       </c>
       <c r="AA16" t="s">
@@ -2341,11 +1957,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29">
       <c r="A17" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>560025</v>
       </c>
       <c r="AA17" t="s">
@@ -2358,11 +1974,11 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29">
       <c r="A18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>40953441</v>
       </c>
       <c r="AA18" t="s">
@@ -2375,11 +1991,11 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29">
       <c r="A19" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="23" t="s">
         <v>228</v>
       </c>
       <c r="AA19" t="s">
@@ -2392,7 +2008,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29">
       <c r="A20" s="17" t="s">
         <v>42</v>
       </c>
@@ -2404,11 +2020,11 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29">
       <c r="A21" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="25"/>
+      <c r="B21" s="24"/>
       <c r="AB21" t="s">
         <v>91</v>
       </c>
@@ -2416,11 +2032,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29">
       <c r="A22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>229</v>
       </c>
       <c r="AB22" t="s">
@@ -2430,7 +2046,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29">
       <c r="A23" s="17" t="s">
         <v>45</v>
       </c>
@@ -2442,11 +2058,11 @@
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29">
       <c r="A24" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="23"/>
+      <c r="B24" s="22"/>
       <c r="AB24" t="s">
         <v>94</v>
       </c>
@@ -2454,11 +2070,11 @@
         <v>152</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29">
       <c r="A25" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="23"/>
+      <c r="B25" s="22"/>
       <c r="AB25" t="s">
         <v>95</v>
       </c>
@@ -2466,11 +2082,11 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29">
       <c r="A26" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="23"/>
+      <c r="B26" s="22"/>
       <c r="AB26" t="s">
         <v>96</v>
       </c>
@@ -2478,11 +2094,11 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29">
       <c r="A27" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="23"/>
+      <c r="B27" s="22"/>
       <c r="AB27" t="s">
         <v>97</v>
       </c>
@@ -2490,11 +2106,11 @@
         <v>155</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29">
       <c r="A28" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="23"/>
+      <c r="B28" s="22"/>
       <c r="AB28" t="s">
         <v>98</v>
       </c>
@@ -2502,11 +2118,11 @@
         <v>156</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29">
       <c r="A29" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="23"/>
+      <c r="B29" s="22"/>
       <c r="AB29" t="s">
         <v>99</v>
       </c>
@@ -2514,11 +2130,11 @@
         <v>157</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29">
       <c r="A30" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="23"/>
+      <c r="B30" s="22"/>
       <c r="AB30" t="s">
         <v>100</v>
       </c>
@@ -2526,11 +2142,11 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29">
       <c r="A31" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="23"/>
+      <c r="B31" s="22"/>
       <c r="AB31" t="s">
         <v>101</v>
       </c>
@@ -2538,11 +2154,11 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
+    <row r="32" spans="1:29">
+      <c r="A32" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="19"/>
+      <c r="B32" s="26"/>
       <c r="AB32" t="s">
         <v>102</v>
       </c>
@@ -2550,11 +2166,11 @@
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29">
       <c r="A33" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="21" t="s">
         <v>230</v>
       </c>
       <c r="AB33" t="s">
@@ -2564,11 +2180,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29">
       <c r="A34" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="25" t="s">
         <v>231</v>
       </c>
       <c r="AB34" t="s">
@@ -2578,11 +2194,11 @@
         <v>162</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29">
       <c r="A35" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="21" t="s">
         <v>232</v>
       </c>
       <c r="AB35" t="s">
@@ -2592,11 +2208,11 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29">
       <c r="A36" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="20">
         <v>14</v>
       </c>
       <c r="AB36" t="s">
@@ -2606,11 +2222,11 @@
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29">
       <c r="A37" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="21"/>
+      <c r="B37" s="20"/>
       <c r="AB37" t="s">
         <v>107</v>
       </c>
@@ -2618,11 +2234,11 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29">
       <c r="A38" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="20" t="s">
         <v>225</v>
       </c>
       <c r="AB38" t="s">
@@ -2632,11 +2248,11 @@
         <v>166</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29">
       <c r="A39" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="20" t="s">
         <v>226</v>
       </c>
       <c r="AB39" t="s">
@@ -2646,11 +2262,11 @@
         <v>167</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29">
       <c r="A40" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="20" t="s">
         <v>227</v>
       </c>
       <c r="AB40" t="s">
@@ -2660,80 +2276,80 @@
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29">
       <c r="A41" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="20" t="s">
         <v>145</v>
       </c>
       <c r="AB41" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29">
       <c r="A42" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="20">
         <v>560025</v>
       </c>
       <c r="AB42" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29">
       <c r="A43" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="20">
         <v>41523562</v>
       </c>
       <c r="AB43" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29">
       <c r="A44" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="23" t="s">
         <v>228</v>
       </c>
       <c r="AB44" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29">
       <c r="A45" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="23"/>
+      <c r="B45" s="22"/>
       <c r="AB45" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29">
       <c r="A46" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="23"/>
+      <c r="B46" s="22"/>
       <c r="AB46" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29">
       <c r="A47" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="20" t="s">
         <v>233</v>
       </c>
       <c r="AB47" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29">
       <c r="A48" s="17" t="s">
         <v>45</v>
       </c>
@@ -2742,73 +2358,73 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28">
       <c r="A49" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="20">
         <v>9845346395</v>
       </c>
       <c r="AB49" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28">
       <c r="AB50" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28">
       <c r="AB51" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28">
       <c r="AB52" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28">
       <c r="AB53" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28">
       <c r="AB54" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28">
       <c r="AB55" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:28">
       <c r="AB56" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:28">
       <c r="AB57" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:28">
       <c r="AB58" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:28">
       <c r="AB59" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:28">
       <c r="AB60" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:28">
       <c r="AB61" t="s">
         <v>131</v>
       </c>
@@ -2820,40 +2436,39 @@
     <mergeCell ref="A32:B32"/>
   </mergeCells>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{9CA7892C-0B9B-47D1-9018-CB0DD5A33844}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4">
       <formula1>$AA$4:$AA$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{9EBF8C94-0FAF-4E02-9FD4-0B96A906D90B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6">
       <formula1>"Quarter 1,Quarter 2,Quarter 3,Quarter 4"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B30" xr:uid="{D99006E8-235B-44B1-8A8A-7F024686F6E3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B30">
       <formula1>$AB$4:$AB$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16 B24 B41" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16 B24 B41">
       <formula1>$AC$4:$AC$40</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{59879ED9-93BD-4C11-B11D-7BCB62564554}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
       <formula1>"2021-22,2020-21,2019-20,2018-19,2017-18,2016-17,2015-16,2014-15,2013-14"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18 B20" xr:uid="{EA87B743-C14D-4148-8A98-40FBD5CFE48E}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18 B20">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B23 B47:B48 B33" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B23 B47:B48 B33">
       <formula1>0</formula1>
       <formula2>75</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:IV7"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" style="5" customWidth="1"/>
@@ -2872,7 +2487,7 @@
     <col min="16" max="16" width="14.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:256" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:256" ht="51" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
@@ -2922,7 +2537,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:256" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:256" ht="13.5" customHeight="1" thickBot="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -3692,7 +3307,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:256" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:256">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3742,7 +3357,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:256" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:256">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -3792,7 +3407,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:256" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:256">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -3842,7 +3457,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:256" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:256">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -3892,7 +3507,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:256" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:256">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -3944,28 +3559,28 @@
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:P2" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:P2">
       <formula1>"µ"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N65536" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N65536">
       <formula1>32874</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M65536" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M65536">
       <formula1>10</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O65536" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="textLength" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O65536">
       <formula1>8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L65536" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L65536">
       <formula1>"200-Payable by Taxpayer,400-Regular Assessment (Raised by I. T. Dept.)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P65536" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P65536">
       <formula1>"Cheque,Cash/ePayment,Transfer Voucher"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A65536 C3:K65536" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A65536 C3:K65536">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B65536" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B65536">
       <formula1>"192-92A,192-92B,192-92C"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3975,18 +3590,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:HD10"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="5" customWidth="1"/>
@@ -4008,7 +3623,7 @@
     <col min="44" max="16384" width="9.140625" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:212" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:212" ht="31.5" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>29</v>
       </c>
@@ -4070,7 +3685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:212" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:212" ht="13.5" customHeight="1" thickBot="1">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -4708,7 +4323,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:212" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:212">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -4764,7 +4379,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:212" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:212">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -4820,7 +4435,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:212" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:212">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -4876,7 +4491,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="1:212" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:212">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -4932,7 +4547,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:212" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:212">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -4988,54 +4603,53 @@
         <v>218</v>
       </c>
     </row>
-    <row r="10" spans="1:212" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:212">
       <c r="B10" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I65536" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I65536">
       <formula1>"192-92A,192-92B,192-92C"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:N65536 P3:P65536" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:N65536 P3:P65536">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O65536" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O65536">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R65536" xr:uid="{00000000-0002-0000-0300-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3:R65536">
       <formula1>"LOWER DEDUCTION U/S 197,NO DEDUCTION U/S 197,PAN Not available - Higher Rate (20%)"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J65536" xr:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J65536">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K65536 Q3:Q65536" xr:uid="{00000000-0002-0000-0300-000005000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K65536 Q3:Q65536">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B65536" xr:uid="{00000000-0002-0000-0300-000006000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B65536">
       <formula1>75</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:G65536" xr:uid="{00000000-0002-0000-0300-000007000000}">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:G65536">
       <formula1>32874</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A65536" xr:uid="{00000000-0002-0000-0300-000008000000}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A65536">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D65536" xr:uid="{00000000-0002-0000-0300-000009000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D65536">
       <formula1>20</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C65536" xr:uid="{00000000-0002-0000-0300-00000A000000}">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C65536">
       <formula1>10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E65536" xr:uid="{00000000-0002-0000-0300-00000B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E65536">
       <formula1>"Women,Senior Citizen,Super Senior Citizen,Others"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:T2" xr:uid="{00000000-0002-0000-0300-00000C000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:T2">
       <formula1>"µ"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>